--- a/r5-TC-FHIR-AG-Scheduling-R5-EncounterClass-QA-errors/StructureDefinition-at-scheduling-schedule.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-EncounterClass-QA-errors/StructureDefinition-at-scheduling-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T14:41:49+00:00</t>
+    <t>2026-03-17T15:39:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
